--- a/data/trans_orig/P68-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P68-Clase-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2007</t>
+          <t>Población según si piensan que su trabajo les afecta negativamente en 2007 (tasa de respuesta: 99,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51911</t>
+          <t>52303</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81329</t>
+          <t>82336</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36455</t>
+          <t>36053</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59736</t>
+          <t>60072</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94116</t>
+          <t>93237</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>134203</t>
+          <t>130230</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276469</t>
+          <t>275462</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>305887</t>
+          <t>305495</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>157408</t>
+          <t>157072</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>180689</t>
+          <t>181091</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>440739</t>
+          <t>444712</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>480826</t>
+          <t>481705</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,78%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31170</t>
+          <t>30619</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57324</t>
+          <t>56070</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30219</t>
+          <t>30759</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54369</t>
+          <t>54180</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68583</t>
+          <t>67612</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101359</t>
+          <t>105674</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>212535</t>
+          <t>213789</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>238689</t>
+          <t>239240</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>179417</t>
+          <t>179606</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>203567</t>
+          <t>203027</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>402286</t>
+          <t>397971</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>435062</t>
+          <t>436033</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,58%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85766</t>
+          <t>83961</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119678</t>
+          <t>121058</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23390</t>
+          <t>23576</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98652</t>
+          <t>98817</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135369</t>
+          <t>135823</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,24%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>258197</t>
+          <t>256817</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>292109</t>
+          <t>293914</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33492</t>
+          <t>33306</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47032</t>
+          <t>47098</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>299387</t>
+          <t>298933</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>336104</t>
+          <t>335939</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,27%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>177019</t>
+          <t>177875</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>225681</t>
+          <t>228482</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39110</t>
+          <t>38484</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65196</t>
+          <t>63561</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>224732</t>
+          <t>224777</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>277945</t>
+          <t>280600</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>475804</t>
+          <t>473003</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>524466</t>
+          <t>523610</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>239805</t>
+          <t>241440</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>265891</t>
+          <t>266517</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>728541</t>
+          <t>725886</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>781754</t>
+          <t>781709</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50473</t>
+          <t>50452</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77432</t>
+          <t>77914</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51714</t>
+          <t>52325</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79817</t>
+          <t>80239</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109881</t>
+          <t>109491</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>149350</t>
+          <t>147819</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105504</t>
+          <t>105022</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132463</t>
+          <t>132484</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>128834</t>
+          <t>128412</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>156937</t>
+          <t>156326</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>242237</t>
+          <t>243768</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>281706</t>
+          <t>282096</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,04%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2438,107 +2438,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472305</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>434785</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>510365</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>215</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220121</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>196389</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>247541</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>665</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692427</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>647587</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>743145</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -2551,107 +2551,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1417648</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1379588</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1455168</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>763</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>801343</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>773923</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>825075</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2218990</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2168272</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2263830</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,76%</t>
         </is>
       </c>
     </row>
@@ -2664,462 +2664,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1889953</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1889953</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1889953</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>978</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1021464</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1021464</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1021464</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2911417</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2911417</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2911417</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>472305</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>434675</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>511692</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>24,99%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>23,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>27,07%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>220121</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>195809</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>249326</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>21,55%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>19,17%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>24,41%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>692427</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>646303</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>737942</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>23,78%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>22,2%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>25,35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>1360</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1417648</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>1378261</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1455278</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>75,01%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>72,93%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>77,0%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>763</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>801343</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>772138</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>825655</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>78,45%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>75,59%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>80,83%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>2123</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>2218990</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>2173475</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>2265114</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>76,22%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>74,65%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>77,8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>1810</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>1889953</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1889953</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1889953</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>978</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>1021464</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>1021464</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1021464</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>2788</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>2911417</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>2911417</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>2911417</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -3129,7 +2786,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3142,7 +2798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3173,7 +2829,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2012</t>
+          <t>Población según si piensan que su trabajo les afecta negativamente en 2012 (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3024,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41120</t>
+          <t>43018</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>70281</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3039,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3059,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32680</t>
+          <t>33241</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57464</t>
+          <t>56768</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3074,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3094,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82762</t>
+          <t>82253</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118456</t>
+          <t>119613</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3109,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3137,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>233688</t>
+          <t>232522</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>261683</t>
+          <t>259785</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3152,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3172,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>136950</t>
+          <t>137646</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>161734</t>
+          <t>161173</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3187,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3207,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>378761</t>
+          <t>377604</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>414455</t>
+          <t>414964</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3222,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3367,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25858</t>
+          <t>26823</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49655</t>
+          <t>51336</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3382,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3402,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17772</t>
+          <t>17666</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38976</t>
+          <t>38355</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3417,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3437,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48859</t>
+          <t>48504</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81664</t>
+          <t>78989</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3452,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3480,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>207877</t>
+          <t>206196</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>231674</t>
+          <t>230709</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3495,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3515,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>128059</t>
+          <t>128680</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>149263</t>
+          <t>149369</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3530,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3550,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>342903</t>
+          <t>345578</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>375708</t>
+          <t>376063</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3565,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,58%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +3710,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64930</t>
+          <t>65678</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95593</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +3725,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +3745,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24030</t>
+          <t>24690</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43552</t>
+          <t>43514</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +3760,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +3780,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95847</t>
+          <t>96498</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132355</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +3795,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,37%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +3823,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>184997</t>
+          <t>185590</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>215660</t>
+          <t>214912</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +3838,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +3858,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67176</t>
+          <t>67214</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86698</t>
+          <t>86038</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +3873,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +3893,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>258963</t>
+          <t>256827</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>295471</t>
+          <t>294820</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +3908,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,34%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4053,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100307</t>
+          <t>99774</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>139143</t>
+          <t>135238</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4068,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4088,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53475</t>
+          <t>53984</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84605</t>
+          <t>83185</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4103,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4123,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>161581</t>
+          <t>161315</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>210551</t>
+          <t>209619</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4138,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4166,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>285749</t>
+          <t>289654</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>324585</t>
+          <t>325118</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4181,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4201,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>216301</t>
+          <t>217721</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>247431</t>
+          <t>246922</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4216,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4236,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>515248</t>
+          <t>516180</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>564218</t>
+          <t>564484</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4251,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,77%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4396,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30667</t>
+          <t>28669</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51654</t>
+          <t>52281</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4411,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4431,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32042</t>
+          <t>33326</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56287</t>
+          <t>56603</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4446,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4466,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68751</t>
+          <t>68442</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99908</t>
+          <t>102834</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4481,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4509,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101234</t>
+          <t>100607</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122221</t>
+          <t>124219</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4524,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4544,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119345</t>
+          <t>119029</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143590</t>
+          <t>142306</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4559,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4579,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>228612</t>
+          <t>225686</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>259769</t>
+          <t>260078</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4594,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,17%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +4719,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5073,107 +4729,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>318</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>331452</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>300958</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>365159</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>198</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>215828</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>190759</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>242807</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>516</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>547280</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>506861</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>591211</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -5186,107 +4842,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1087253</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1053546</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1117747</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>678</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>732888</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>705909</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>757957</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1692</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1820141</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1776210</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1860560</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,59%</t>
         </is>
       </c>
     </row>
@@ -5299,462 +4955,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1418705</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1418705</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1418705</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>876</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>948716</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>948716</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>948716</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2367421</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2367421</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2367421</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>331452</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>300778</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>363978</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>23,36%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>21,2%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>25,66%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>215828</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>190384</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>244971</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>22,75%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>20,07%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>25,82%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>516</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>547280</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>506992</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>587553</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>23,12%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>21,42%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>24,82%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>1014</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1087253</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>1054727</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1117927</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>76,64%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>74,34%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>78,8%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>732888</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>703745</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>758332</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>77,25%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>74,18%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>79,93%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1692</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1820141</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1779868</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1860429</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>76,88%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>75,18%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>78,58%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>1332</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>1418705</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1418705</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1418705</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>876</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>948716</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>948716</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>948716</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>2208</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>2367421</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>2367421</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>2367421</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -5764,7 +5077,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5777,7 +5089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5808,7 +5120,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2016</t>
+          <t>Población según si piensan que su trabajo les afecta negativamente en 2016 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +5315,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33655</t>
+          <t>35589</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62050</t>
+          <t>62950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +5330,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +5350,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35087</t>
+          <t>35464</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60726</t>
+          <t>59768</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +5365,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +5385,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77357</t>
+          <t>76544</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112151</t>
+          <t>111270</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +5400,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +5428,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>215217</t>
+          <t>214317</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>243612</t>
+          <t>241678</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +5443,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +5463,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>151315</t>
+          <t>152273</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>176954</t>
+          <t>176577</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +5478,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +5498,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>377157</t>
+          <t>378038</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>411951</t>
+          <t>412764</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +5513,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,36%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +5658,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21072</t>
+          <t>21048</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42493</t>
+          <t>43370</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +5673,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +5693,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20272</t>
+          <t>20508</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40464</t>
+          <t>40002</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +5708,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +5728,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45823</t>
+          <t>46378</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77192</t>
+          <t>75234</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +5743,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +5771,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>200616</t>
+          <t>199739</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>222037</t>
+          <t>222061</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +5786,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +5806,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>147770</t>
+          <t>148232</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>167962</t>
+          <t>167726</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +5821,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +5841,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>354152</t>
+          <t>356110</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>385521</t>
+          <t>384966</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +5856,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,25%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6001,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52228</t>
+          <t>52839</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81480</t>
+          <t>80794</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6016,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6036,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>16537</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6051,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6071,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62226</t>
+          <t>61172</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92067</t>
+          <t>91840</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6086,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,58%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6114,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133186</t>
+          <t>133872</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>162438</t>
+          <t>161827</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6129,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6149,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50266</t>
+          <t>50663</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62208</t>
+          <t>62421</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6164,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6184,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>189799</t>
+          <t>190026</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>219640</t>
+          <t>220694</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6199,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>78,3%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +6344,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>116356</t>
+          <t>115887</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157652</t>
+          <t>157622</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +6359,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +6379,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68197</t>
+          <t>68142</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102203</t>
+          <t>100444</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +6394,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +6414,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>195711</t>
+          <t>196428</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>246877</t>
+          <t>247850</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +6429,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +6457,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>324672</t>
+          <t>324702</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365968</t>
+          <t>366437</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +6472,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +6492,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>264801</t>
+          <t>266560</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>298807</t>
+          <t>298862</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +6507,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +6527,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>602451</t>
+          <t>601478</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>653617</t>
+          <t>652900</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +6542,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,87%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +6687,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56677</t>
+          <t>55740</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82693</t>
+          <t>83388</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +6702,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +6722,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36278</t>
+          <t>35664</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60861</t>
+          <t>58927</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +6737,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +6757,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99075</t>
+          <t>97591</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134294</t>
+          <t>134374</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +6772,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,49%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +6800,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110278</t>
+          <t>109583</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>136294</t>
+          <t>137231</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +6815,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +6835,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135761</t>
+          <t>137695</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>160344</t>
+          <t>160958</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +6850,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +6870,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>255299</t>
+          <t>255219</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>290518</t>
+          <t>292002</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +6885,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,95%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7010,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7708,107 +7020,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>322</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350001</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>316701</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>384864</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>207</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216298</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>191391</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>243020</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>529</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566299</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>524653</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>608912</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -7821,107 +7133,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>990</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1060336</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1025473</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1093636</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>800</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>814803</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>788081</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>839710</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1875139</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1832526</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1916785</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,51%</t>
         </is>
       </c>
     </row>
@@ -7934,462 +7246,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1410337</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1410337</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1410337</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1031101</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1031101</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1031101</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2441438</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2441438</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2441438</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>350001</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>318451</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>384700</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>24,82%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>22,58%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>27,28%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>216298</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>192722</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>242708</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>20,98%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>18,69%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>23,54%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>566299</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>526758</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>611851</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>23,2%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>21,58%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>25,06%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>990</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1060336</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>1025637</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1091886</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>75,18%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>72,72%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>77,42%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>814803</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>788393</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>838379</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>79,02%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>76,46%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>81,31%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1790</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1875139</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1829587</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1914680</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>76,8%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>74,94%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>78,42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>1312</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>1410337</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1410337</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1410337</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1007</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>1031101</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>1031101</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1031101</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>2319</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>2441438</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>2441438</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>2441438</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -8399,7 +7368,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8412,7 +7380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8443,7 +7411,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2023</t>
+          <t>Población según si piensan que su trabajo les afecta negativamente en 2023 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +7606,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33270</t>
+          <t>35409</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60120</t>
+          <t>59743</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +7621,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +7641,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48345</t>
+          <t>48491</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73091</t>
+          <t>72364</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +7656,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +7676,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89479</t>
+          <t>87942</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>124255</t>
+          <t>124379</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +7691,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +7719,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>283811</t>
+          <t>284188</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310661</t>
+          <t>308522</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +7734,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +7754,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>241289</t>
+          <t>242016</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>266035</t>
+          <t>265889</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +7769,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +7789,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>534056</t>
+          <t>533932</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>568832</t>
+          <t>570369</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +7804,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,64%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +7949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37379</t>
+          <t>37785</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64897</t>
+          <t>65803</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +7964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +7984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32492</t>
+          <t>32243</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55267</t>
+          <t>55008</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +7999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +8019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76865</t>
+          <t>76708</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110352</t>
+          <t>110839</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +8034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +8062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>235335</t>
+          <t>234429</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>262853</t>
+          <t>262447</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +8077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +8097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193410</t>
+          <t>193669</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>216185</t>
+          <t>216434</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +8112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +8132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>438558</t>
+          <t>438071</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>472045</t>
+          <t>472202</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +8147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,03%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +8292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14359</t>
+          <t>12734</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>124036</t>
+          <t>126754</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +8307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +8327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12555</t>
+          <t>12064</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24600</t>
+          <t>24556</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +8342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +8362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21172</t>
+          <t>26032</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>144510</t>
+          <t>143960</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +8377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +8405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>363061</t>
+          <t>360343</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>472738</t>
+          <t>474363</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +8420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +8440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47073</t>
+          <t>47117</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59118</t>
+          <t>59609</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +8455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +8475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>414261</t>
+          <t>414811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>537599</t>
+          <t>532739</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +8490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +8635,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>112595</t>
+          <t>110989</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157344</t>
+          <t>156468</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +8650,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +8670,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90913</t>
+          <t>91318</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>120712</t>
+          <t>122675</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +8685,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +8705,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>214623</t>
+          <t>211090</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>270182</t>
+          <t>266314</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +8720,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,37%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +8748,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>394570</t>
+          <t>395446</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>439319</t>
+          <t>440925</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +8763,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +8783,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>300366</t>
+          <t>298403</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>330165</t>
+          <t>329760</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +8798,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +8818,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>702810</t>
+          <t>706678</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>758369</t>
+          <t>761902</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +8833,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>78,31%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +8978,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39207</t>
+          <t>39417</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66160</t>
+          <t>69173</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +8993,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +9013,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76804</t>
+          <t>69393</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>192341</t>
+          <t>184716</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +9028,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +9048,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124652</t>
+          <t>126210</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>244157</t>
+          <t>245869</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +9063,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,88%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +9091,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167199</t>
+          <t>164186</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194152</t>
+          <t>193942</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +9106,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +9126,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175776</t>
+          <t>183401</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>291313</t>
+          <t>298724</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +9141,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +9161,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>357319</t>
+          <t>355607</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>476824</t>
+          <t>475266</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +9176,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,02%</t>
         </is>
       </c>
     </row>
@@ -10333,7 +9301,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10343,107 +9311,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>338</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339505</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220486</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>403355</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>471</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352292</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>301172</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>438530</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>809</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>691797</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>542552</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>795463</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -10456,107 +9424,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1577028</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1513178</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1696047</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1071634</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>985396</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1122754</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2648662</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2544996</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2797907</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,76%</t>
         </is>
       </c>
     </row>
@@ -10569,462 +9537,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1916533</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1916533</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1916533</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1423926</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1423926</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1423926</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3340459</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3340459</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3340459</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>339505</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>204144</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>404121</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>17,71%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>10,65%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>21,09%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>352292</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>300271</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>432237</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>24,74%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>21,09%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>30,36%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>809</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>691797</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>541036</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>788807</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>20,71%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>16,2%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>23,61%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>1292</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1577028</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>1512412</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1712389</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>82,29%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>78,91%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>89,35%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1071634</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>991689</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>1123655</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>75,26%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>69,64%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>78,91%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>2795</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>2648662</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>2551652</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>2799423</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>79,29%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>76,39%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>83,8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>1630</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>1916533</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1916533</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1916533</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>1423926</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>1423926</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1423926</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3604</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3340459</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3340459</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3340459</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -11034,7 +9659,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_orig/P68-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P68-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52303</t>
+          <t>50159</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82336</t>
+          <t>80090</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,82 +748,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>22,38%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>46650</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>35585</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>59672</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>21,48%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>16,39%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>27,48%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>111733</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>92158</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>132300</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>19,43%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>16,03%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>23,01%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>46650</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>36053</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>60072</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>21,48%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>16,6%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>27,66%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>111733</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>93237</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>130230</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>19,43%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>16,22%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275462</t>
+          <t>277708</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>305495</t>
+          <t>307639</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,82 +861,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>77,62%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>85,98%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>170494</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>157472</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>181559</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>78,52%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>72,52%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>83,61%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>463209</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>442642</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>482784</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>80,57%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>76,99%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>85,38%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>170494</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>157072</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>181091</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>78,52%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>72,34%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>83,4%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>447</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>463209</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>444712</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>481705</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>80,57%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>77,35%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,97%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30619</t>
+          <t>30593</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56070</t>
+          <t>55442</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30759</t>
+          <t>30507</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54180</t>
+          <t>53285</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67612</t>
+          <t>69338</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105674</t>
+          <t>102541</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>213789</t>
+          <t>214417</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>239240</t>
+          <t>239266</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>179606</t>
+          <t>180501</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>203027</t>
+          <t>203279</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>397971</t>
+          <t>401104</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>436033</t>
+          <t>434307</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,23%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83961</t>
+          <t>83982</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121058</t>
+          <t>119678</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9784</t>
+          <t>9826</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23576</t>
+          <t>23508</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98817</t>
+          <t>97806</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135823</t>
+          <t>135134</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,08%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>256817</t>
+          <t>258197</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>293914</t>
+          <t>293893</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33306</t>
+          <t>33374</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47098</t>
+          <t>47056</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>298933</t>
+          <t>299622</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>335939</t>
+          <t>336950</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,5%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>177875</t>
+          <t>178927</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>228482</t>
+          <t>228313</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38484</t>
+          <t>38690</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63561</t>
+          <t>63237</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>224777</t>
+          <t>224023</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>280600</t>
+          <t>280557</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>473003</t>
+          <t>473172</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>523610</t>
+          <t>522558</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>241440</t>
+          <t>241764</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>266517</t>
+          <t>266311</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>725886</t>
+          <t>725929</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>781709</t>
+          <t>782463</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,74%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50452</t>
+          <t>51300</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77914</t>
+          <t>78732</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52325</t>
+          <t>52576</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80239</t>
+          <t>81097</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109491</t>
+          <t>111187</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>147819</t>
+          <t>149001</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>38,05%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105022</t>
+          <t>104204</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132484</t>
+          <t>131636</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>128412</t>
+          <t>127554</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>156326</t>
+          <t>156075</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>243768</t>
+          <t>242586</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>282096</t>
+          <t>280400</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,61%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>434785</t>
+          <t>435450</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>510365</t>
+          <t>511111</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>196389</t>
+          <t>190991</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>247541</t>
+          <t>247029</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>647587</t>
+          <t>648881</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>743145</t>
+          <t>735848</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1379588</t>
+          <t>1378842</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1455168</t>
+          <t>1454503</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>773923</t>
+          <t>774435</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>825075</t>
+          <t>830473</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2168272</t>
+          <t>2175569</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2263830</t>
+          <t>2262536</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,71%</t>
         </is>
       </c>
     </row>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43018</t>
+          <t>41564</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70281</t>
+          <t>70097</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33241</t>
+          <t>32644</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56768</t>
+          <t>57123</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82253</t>
+          <t>80965</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>119613</t>
+          <t>117703</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3109,12 +3109,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -3137,12 +3137,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>232522</t>
+          <t>232706</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>259785</t>
+          <t>261239</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>137646</t>
+          <t>137291</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>161173</t>
+          <t>161770</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>377604</t>
+          <t>379514</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>414964</t>
+          <t>416252</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,72%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26823</t>
+          <t>26569</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51336</t>
+          <t>50562</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17666</t>
+          <t>17507</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38355</t>
+          <t>38277</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48504</t>
+          <t>51052</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78989</t>
+          <t>80618</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>206196</t>
+          <t>206970</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>230709</t>
+          <t>230963</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>128680</t>
+          <t>128758</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>149369</t>
+          <t>149528</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>345578</t>
+          <t>343949</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>376063</t>
+          <t>373515</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>87,98%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65678</t>
+          <t>66235</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95000</t>
+          <t>96507</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24690</t>
+          <t>23801</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43514</t>
+          <t>44232</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96498</t>
+          <t>96812</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>132834</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>33,95%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>185590</t>
+          <t>184083</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>214912</t>
+          <t>214355</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67214</t>
+          <t>66496</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86038</t>
+          <t>86927</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>256827</t>
+          <t>258484</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>294820</t>
+          <t>294506</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,26%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>99774</t>
+          <t>99106</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>135238</t>
+          <t>138019</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53984</t>
+          <t>54266</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83185</t>
+          <t>83789</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>161315</t>
+          <t>162798</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>209619</t>
+          <t>214124</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,5%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>289654</t>
+          <t>286873</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>325118</t>
+          <t>325786</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>217721</t>
+          <t>217117</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>246922</t>
+          <t>246640</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>516180</t>
+          <t>511675</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>564484</t>
+          <t>563001</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,57%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28669</t>
+          <t>29518</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52281</t>
+          <t>52079</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33326</t>
+          <t>32604</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56603</t>
+          <t>56736</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68442</t>
+          <t>69307</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102834</t>
+          <t>103250</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100607</t>
+          <t>100809</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>124219</t>
+          <t>123370</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119029</t>
+          <t>118896</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142306</t>
+          <t>143028</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>225686</t>
+          <t>225270</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>260078</t>
+          <t>259213</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>78,9%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>300958</t>
+          <t>298880</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>365159</t>
+          <t>363016</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>190759</t>
+          <t>190709</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>242807</t>
+          <t>245637</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>506861</t>
+          <t>505548</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>591211</t>
+          <t>585496</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1053546</t>
+          <t>1055689</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1117747</t>
+          <t>1119825</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>705909</t>
+          <t>703079</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>757957</t>
+          <t>758007</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1776210</t>
+          <t>1781925</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1860560</t>
+          <t>1861873</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,65%</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35589</t>
+          <t>35905</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62950</t>
+          <t>60521</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35464</t>
+          <t>34780</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59768</t>
+          <t>58943</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5385,12 +5385,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76544</t>
+          <t>75491</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111270</t>
+          <t>110311</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>214317</t>
+          <t>216746</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>241678</t>
+          <t>241362</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152273</t>
+          <t>153098</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>176577</t>
+          <t>177261</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>378038</t>
+          <t>378997</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>412764</t>
+          <t>413817</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -5658,12 +5658,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21048</t>
+          <t>20886</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43370</t>
+          <t>42201</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20508</t>
+          <t>20297</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40002</t>
+          <t>40875</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5728,12 +5728,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46378</t>
+          <t>46665</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75234</t>
+          <t>75241</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>199739</t>
+          <t>200908</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>222061</t>
+          <t>222223</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>148232</t>
+          <t>147359</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>167726</t>
+          <t>167937</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>356110</t>
+          <t>356103</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>384966</t>
+          <t>384679</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,18%</t>
         </is>
       </c>
     </row>
@@ -6001,12 +6001,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52839</t>
+          <t>52846</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80794</t>
+          <t>82352</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16537</t>
+          <t>16754</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6071,12 +6071,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61172</t>
+          <t>61736</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91840</t>
+          <t>91650</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6086,12 +6086,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,52%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133872</t>
+          <t>132314</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>161827</t>
+          <t>161820</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50663</t>
+          <t>50446</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62421</t>
+          <t>62227</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>190026</t>
+          <t>190216</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>220694</t>
+          <t>220130</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,1%</t>
         </is>
       </c>
     </row>
@@ -6344,12 +6344,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>115887</t>
+          <t>115645</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157622</t>
+          <t>157954</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68142</t>
+          <t>68659</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>100444</t>
+          <t>101738</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>196428</t>
+          <t>195186</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>247850</t>
+          <t>249626</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,39%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>324702</t>
+          <t>324370</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>366437</t>
+          <t>366679</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>266560</t>
+          <t>265266</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>298862</t>
+          <t>298345</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>601478</t>
+          <t>599702</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>652900</t>
+          <t>654142</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>77,02%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55740</t>
+          <t>55802</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83388</t>
+          <t>82671</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35664</t>
+          <t>36184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58927</t>
+          <t>59358</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>97591</t>
+          <t>97652</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134374</t>
+          <t>136269</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,98%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>109583</t>
+          <t>110300</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>137231</t>
+          <t>137169</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>137695</t>
+          <t>137264</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>160958</t>
+          <t>160438</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>255219</t>
+          <t>253324</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>292002</t>
+          <t>291941</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,93%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>316701</t>
+          <t>315797</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>384864</t>
+          <t>384409</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>191391</t>
+          <t>190079</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>243020</t>
+          <t>242483</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>524653</t>
+          <t>525395</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>608912</t>
+          <t>610353</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -7143,12 +7143,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1025473</t>
+          <t>1025928</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1093636</t>
+          <t>1094540</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>788081</t>
+          <t>788618</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>839710</t>
+          <t>841022</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1832526</t>
+          <t>1831085</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1916785</t>
+          <t>1916043</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7228,12 +7228,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,48%</t>
         </is>
       </c>
     </row>
@@ -7601,32 +7601,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>45816</t>
+          <t>52038</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35409</t>
+          <t>38557</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59743</t>
+          <t>68991</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7636,32 +7636,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>59290</t>
+          <t>62032</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48491</t>
+          <t>51804</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72364</t>
+          <t>77465</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7671,32 +7671,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>105106</t>
+          <t>114070</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>87942</t>
+          <t>94832</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>124379</t>
+          <t>135052</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -7714,32 +7714,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>298115</t>
+          <t>322640</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>284188</t>
+          <t>305687</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>308522</t>
+          <t>336121</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7749,32 +7749,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>255090</t>
+          <t>273798</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>242016</t>
+          <t>258365</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>265889</t>
+          <t>284026</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7784,32 +7784,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>553205</t>
+          <t>596438</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>533932</t>
+          <t>575456</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>570369</t>
+          <t>615676</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,65%</t>
         </is>
       </c>
     </row>
@@ -7827,17 +7827,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>343931</t>
+          <t>374678</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>343931</t>
+          <t>374678</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>343931</t>
+          <t>374678</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7862,17 +7862,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>314380</t>
+          <t>335830</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>314380</t>
+          <t>335830</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>314380</t>
+          <t>335830</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7897,17 +7897,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>658311</t>
+          <t>710508</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>658311</t>
+          <t>710508</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>658311</t>
+          <t>710508</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7944,32 +7944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50778</t>
+          <t>52059</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37785</t>
+          <t>37433</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65803</t>
+          <t>66738</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7979,32 +7979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42158</t>
+          <t>45454</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32243</t>
+          <t>35790</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55008</t>
+          <t>56989</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8014,32 +8014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>92937</t>
+          <t>97513</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76708</t>
+          <t>80256</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110839</t>
+          <t>116413</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -8057,32 +8057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>249454</t>
+          <t>265573</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>234429</t>
+          <t>250894</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>262447</t>
+          <t>280199</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8092,32 +8092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>206519</t>
+          <t>224631</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193669</t>
+          <t>213096</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>216434</t>
+          <t>234295</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8127,32 +8127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>455973</t>
+          <t>490204</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>438071</t>
+          <t>471304</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>472202</t>
+          <t>507461</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,34%</t>
         </is>
       </c>
     </row>
@@ -8170,17 +8170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>300232</t>
+          <t>317632</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>300232</t>
+          <t>317632</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>300232</t>
+          <t>317632</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8205,17 +8205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>248677</t>
+          <t>270085</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>248677</t>
+          <t>270085</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>248677</t>
+          <t>270085</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8240,17 +8240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>548910</t>
+          <t>587717</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>548910</t>
+          <t>587717</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>548910</t>
+          <t>587717</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8287,32 +8287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>58523</t>
+          <t>61485</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12734</t>
+          <t>45731</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>126754</t>
+          <t>77325</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8322,32 +8322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17839</t>
+          <t>20457</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>14238</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24556</t>
+          <t>27612</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8357,32 +8357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>76362</t>
+          <t>81942</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26032</t>
+          <t>66110</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143960</t>
+          <t>99828</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -8400,32 +8400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>428574</t>
+          <t>207458</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>360343</t>
+          <t>191618</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>474363</t>
+          <t>223212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8435,32 +8435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>53834</t>
+          <t>60373</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47117</t>
+          <t>53218</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59609</t>
+          <t>66592</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8470,32 +8470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>482409</t>
+          <t>267831</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>414811</t>
+          <t>249945</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>532739</t>
+          <t>283663</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>81,1%</t>
         </is>
       </c>
     </row>
@@ -8513,17 +8513,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>487097</t>
+          <t>268943</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>487097</t>
+          <t>268943</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>487097</t>
+          <t>268943</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8548,17 +8548,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>71673</t>
+          <t>80830</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>71673</t>
+          <t>80830</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71673</t>
+          <t>80830</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8583,17 +8583,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>558771</t>
+          <t>349773</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>558771</t>
+          <t>349773</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>558771</t>
+          <t>349773</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8630,32 +8630,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>133218</t>
+          <t>153762</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>110989</t>
+          <t>132184</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>156468</t>
+          <t>179237</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8665,32 +8665,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>105758</t>
+          <t>113765</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91318</t>
+          <t>98475</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122675</t>
+          <t>130617</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8700,27 +8700,27 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>238976</t>
+          <t>267527</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>211090</t>
+          <t>239977</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>266314</t>
+          <t>297019</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -8743,32 +8743,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>418696</t>
+          <t>459299</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>395446</t>
+          <t>433824</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>480877</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8778,32 +8778,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>315320</t>
+          <t>358509</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>298403</t>
+          <t>341657</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>329760</t>
+          <t>373799</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8813,22 +8813,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>734016</t>
+          <t>817808</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>706678</t>
+          <t>788316</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>761902</t>
+          <t>845358</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>77,89%</t>
         </is>
       </c>
     </row>
@@ -8856,17 +8856,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>551914</t>
+          <t>613061</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>551914</t>
+          <t>613061</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>551914</t>
+          <t>613061</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8891,17 +8891,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>421078</t>
+          <t>472274</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>421078</t>
+          <t>472274</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>421078</t>
+          <t>472274</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8926,17 +8926,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>972992</t>
+          <t>1085335</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>972992</t>
+          <t>1085335</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>972992</t>
+          <t>1085335</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8973,32 +8973,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>51170</t>
+          <t>65666</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39417</t>
+          <t>51030</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69173</t>
+          <t>84545</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9008,32 +9008,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>127247</t>
+          <t>101653</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69393</t>
+          <t>87434</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>184716</t>
+          <t>115863</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9043,32 +9043,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>178417</t>
+          <t>167319</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126210</t>
+          <t>145701</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>245869</t>
+          <t>188871</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -9086,32 +9086,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>182189</t>
+          <t>237210</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164186</t>
+          <t>218331</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193942</t>
+          <t>251846</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9121,32 +9121,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>240870</t>
+          <t>205659</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>183401</t>
+          <t>191449</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>298724</t>
+          <t>219878</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9156,32 +9156,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>423059</t>
+          <t>442869</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>355607</t>
+          <t>421317</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>475266</t>
+          <t>464487</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>76,12%</t>
         </is>
       </c>
     </row>
@@ -9199,17 +9199,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>233359</t>
+          <t>302876</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>233359</t>
+          <t>302876</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>233359</t>
+          <t>302876</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9234,17 +9234,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>368117</t>
+          <t>307312</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>368117</t>
+          <t>307312</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>368117</t>
+          <t>307312</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9269,17 +9269,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>601476</t>
+          <t>610188</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>601476</t>
+          <t>610188</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>601476</t>
+          <t>610188</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9316,32 +9316,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>339505</t>
+          <t>385010</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>220486</t>
+          <t>345408</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>403355</t>
+          <t>424488</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9351,32 +9351,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>352292</t>
+          <t>343362</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>301172</t>
+          <t>313838</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>438530</t>
+          <t>372434</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9386,32 +9386,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>691797</t>
+          <t>728371</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>542552</t>
+          <t>685733</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>795463</t>
+          <t>774905</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -9429,32 +9429,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1577028</t>
+          <t>1492179</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1513178</t>
+          <t>1452701</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1696047</t>
+          <t>1531781</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9464,32 +9464,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1071634</t>
+          <t>1122969</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>985396</t>
+          <t>1093897</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1122754</t>
+          <t>1152493</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9499,32 +9499,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2648662</t>
+          <t>2615150</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2544996</t>
+          <t>2568616</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2797907</t>
+          <t>2657788</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>79,49%</t>
         </is>
       </c>
     </row>
@@ -9542,17 +9542,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1916533</t>
+          <t>1877189</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1916533</t>
+          <t>1877189</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1916533</t>
+          <t>1877189</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9577,17 +9577,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1423926</t>
+          <t>1466331</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1423926</t>
+          <t>1466331</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1423926</t>
+          <t>1466331</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9612,17 +9612,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3340459</t>
+          <t>3343521</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3340459</t>
+          <t>3343521</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3340459</t>
+          <t>3343521</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">

--- a/data/trans_orig/P68-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P68-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2007 (tasa de respuesta: 99,11%)</t>
+          <t>Población según si piensan que su trabajo afecta negativamente a su salud en 2007 (tasa de respuesta: 99,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2829,7 +2829,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2012 (tasa de respuesta: 99,41%)</t>
+          <t>Población según si piensan que su trabajo afecta negativamente a su salud en 2012 (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5120,7 +5120,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2016 (tasa de respuesta: 99,32%)</t>
+          <t>Población según si piensan que su trabajo afecta negativamente a su salud en 2016 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7411,7 +7411,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2023 (tasa de respuesta: 98,55%)</t>
+          <t>Población según si piensan que su trabajo afecta negativamente a su salud en 2023 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
